--- a/msgweb/uploads/contatos.xlsx
+++ b/msgweb/uploads/contatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,15 +434,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Enviado</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>DataEnvio</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Invalido</t>
         </is>
@@ -454,27 +459,157 @@
           <t>Mauricio</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>19994229146</t>
-        </is>
+      <c r="B2" t="n">
+        <v>19994229146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>testeee</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>C:\Users\mauri\OneDrive\Documentos\message_whatsapp\msgweb\uploads\media\ingresso-MAURICIO-FURLAN.png, C:\Users\mauri\OneDrive\Documentos\message_whatsapp\msgweb\uploads\media\WhatsApp Image 2026-07-10 at 12.56.51.jpeg</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-07-12 17:36:21</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-07-25 14:50:39</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mau Mau</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>19994229146</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>outra teste</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-25 13:27:33</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mauuzinho</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>19994229146</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>opa opa , meu nome é goku</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-25 13:27:33</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>super teste do mmau</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>19994229146</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>maumau teste boa! eu não sou um robo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-25 13:27:33</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>19994229146</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>aewwww isso ism deu certo!</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-25 13:27:33</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>19994229146</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bom dia meu bebe!</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-25 13:27:33</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/msgweb/uploads/contatos.xlsx
+++ b/msgweb/uploads/contatos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-14 12:46:23</t>
+          <t>2026-08-15 10:32:36</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-14 12:47:10</t>
+          <t>2026-08-20 11:20:20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-14 12:48:10</t>
+          <t>2026-08-20 11:21:19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -571,8 +571,16 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:24:25</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
@@ -594,8 +602,16 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:25:37</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
@@ -613,8 +629,16 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:26:29</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
@@ -632,8 +656,16 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:28:43</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
@@ -651,8 +683,16 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:31:32</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
@@ -678,8 +718,16 @@
           <t>test_media/teste_azul.png</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:33:42</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
@@ -705,8 +753,16 @@
           <t>test_media/teste_vermelho.jpg</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:35:02</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
@@ -732,8 +788,16 @@
           <t>test_media/teste_grande.png</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:36:26</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
@@ -917,8 +981,16 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Coluna Número vazia. Preencha com DDD + telefone.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -938,8 +1010,16 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Coluna Número vazia. Preencha com DDD + telefone.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -961,8 +1041,16 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Número com menos de 10 dígitos. Confira DDD + telefone.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -984,8 +1072,16 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Número com menos de 10 dígitos. Confira DDD + telefone.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -1179,8 +1275,16 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Número não encontrado no WhatsApp (timeout ao abrir conversa).</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -1518,7 +1622,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Primeiro Duplicado</t>
+          <t>Teste Emojis</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1526,7 +1630,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Número duplicado do Carlos Silva. No upload, este deve ser REMOVIDO (o primeiro vence).</t>
+          <t>Oi {nome}! 😀🎉🚀💪🔥✨👏❤️🙏😎
+Testando emojis variados:
+🌟 Estrela
+🎯 Alvo
+💡 Ideia
+🏆 Troféu
+📱 Celular
+✅ Check
+Emoticons clássicos: :) ;) :D XD &lt;3 :P
+Emojis de bandeira: 🇧🇷🇺🇸🇪🇸
+Família: 👨‍👩‍👧‍👦
+Animais: 🐶🐱🦁🐸🦋
+Se tudo chegou certinho, o envio de emojis está OK! 🎊👍</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1538,6 +1654,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Primeiro Duplicado</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>19994229146</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Número duplicado do Carlos Silva. No upload, este deve ser REMOVIDO (o primeiro vence).</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
